--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -1,132 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ÖZET" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VERİLER" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BIST" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>İşlem ID</t>
-  </si>
-  <si>
-    <t>Hisse</t>
-  </si>
-  <si>
-    <t>Sektör</t>
-  </si>
-  <si>
-    <t>AL Tarihi</t>
-  </si>
-  <si>
-    <t>AL Gücü</t>
-  </si>
-  <si>
-    <t>Giriş Fiyatı</t>
-  </si>
-  <si>
-    <t>Stop Fiyatı</t>
-  </si>
-  <si>
-    <t>Durum</t>
-  </si>
-  <si>
-    <t>Çıkış Tarihi</t>
-  </si>
-  <si>
-    <t>Çıkış Fiyatı</t>
-  </si>
-  <si>
-    <t>Çıkış Nedeni</t>
-  </si>
-  <si>
-    <t>Güncel Fiyat</t>
-  </si>
-  <si>
-    <t>Gerçekleşen Getiri (%)</t>
-  </si>
-  <si>
-    <t>Güncel Getiri (%)</t>
-  </si>
-  <si>
-    <t>Pozisyonda Gün</t>
-  </si>
-  <si>
-    <t>En Yüksek Fiyat</t>
-  </si>
-  <si>
-    <t>En Düşük Fiyat</t>
-  </si>
-  <si>
-    <t>MFE (%)</t>
-  </si>
-  <si>
-    <t>MAE (%)</t>
-  </si>
-  <si>
-    <t>BIST Giriş</t>
-  </si>
-  <si>
-    <t>BIST Çıkış</t>
-  </si>
-  <si>
-    <t>BIST Getiri (%)</t>
-  </si>
-  <si>
-    <t>Alpha (%)</t>
-  </si>
-  <si>
-    <t>Stop Sonrası Güncel (%)</t>
-  </si>
-  <si>
-    <t>Not</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Light"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -134,47 +44,90 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Teması">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -216,7 +169,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -248,10 +201,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -283,7 +235,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -459,116 +410,322 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Alan</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Değer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Son Güncelleme</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>21.08.2026 11:25:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Veri Kaynağı</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>tradingview</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Fallback</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Yeni AL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Güncellenen Satır</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Yeni Kapanan İşlem</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Toplam İşlem</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Açık İşlem</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STOP İşlem</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KAR STOP İşlem</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Script Versiyon</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>tarama.py 2026-08-21 ESv2-revised-tracker</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Y1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>İşlem ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Hisse</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Sektör</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>AL Tarihi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>AL Gücü</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Giriş Fiyatı</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Stop Fiyatı</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Çıkış Tarihi</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Çıkış Fiyatı</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Çıkış Nedeni</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Güncel Fiyat</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Gerçekleşen Getiri (%)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Güncel Getiri (%)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Pozisyonda Gün</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>En Yüksek Fiyat</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>En Düşük Fiyat</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>MFE (%)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>MAE (%)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>BIST Giriş</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>BIST Çıkış</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>BIST Getiri (%)</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Alpha (%)</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Stop Sonrası Güncel (%)</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Not</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tarih</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Açılış</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Kapanış</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Günlük Değişim</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.08.2026 20:53:43</t>
+          <t>24.08.2026 20:54:13</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>241.4</v>
+        <v>240</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-2.23</v>
+        <v>-2.79</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
         <v>249</v>
@@ -838,6 +838,79 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ISLEM-000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MARKA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GUCLU AL</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>87</v>
+      </c>
+      <c r="G4" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>87</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>87</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>14501.49</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.08.2026 20:54:13</t>
+          <t>25.08.2026 20:53:48</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -728,26 +728,26 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>240</v>
+        <v>239.9</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-2.79</v>
+        <v>-2.84</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P2" t="n">
         <v>249</v>
       </c>
       <c r="Q2" t="n">
-        <v>238.4</v>
+        <v>237.9</v>
       </c>
       <c r="R2" t="n">
         <v>0.85</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.44</v>
+        <v>-3.65</v>
       </c>
       <c r="T2" t="n">
         <v>14274.02</v>
@@ -874,26 +874,26 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>87</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q4" t="n">
-        <v>87</v>
+        <v>84.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2.53</v>
       </c>
       <c r="T4" t="n">
         <v>14501.49</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.08.2026 20:53:48</t>
+          <t>26.08.2026 20:54:03</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y4"/>
+  <dimension ref="A1:Y5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>239.9</v>
+        <v>245.8</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-2.84</v>
+        <v>-0.45</v>
       </c>
       <c r="O2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>249</v>
@@ -874,26 +874,26 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>86.40000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.8</v>
+        <v>84.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.15</v>
+        <v>2.07</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.53</v>
+        <v>-3.22</v>
       </c>
       <c r="T4" t="n">
         <v>14501.49</v>
@@ -907,6 +907,79 @@
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ISLEM-000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TERA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>180.7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14610.92</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.08.2026 20:54:03</t>
+          <t>27.08.2026 20:53:47</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -728,23 +728,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>245.8</v>
+        <v>248.6</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q2" t="n">
         <v>237.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0.85</v>
+        <v>2.07</v>
       </c>
       <c r="S2" t="n">
         <v>-3.65</v>
@@ -874,23 +874,23 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>88.15000000000001</v>
+        <v>86.25</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1.32</v>
+        <v>-0.86</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>88.8</v>
+        <v>90</v>
       </c>
       <c r="Q4" t="n">
         <v>84.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2.07</v>
+        <v>3.45</v>
       </c>
       <c r="S4" t="n">
         <v>-3.22</v>
@@ -947,23 +947,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>180.7</v>
+        <v>185</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>180.7</v>
+        <v>187.5</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27.08.2026 20:53:47</t>
+          <t>28.08.2026 20:53:43</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>248.6</v>
+        <v>242.2</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.9</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P2" t="n">
         <v>252</v>
@@ -867,33 +867,41 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>46262.375</v>
+      </c>
+      <c r="J4" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>86.25</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>-0.86</v>
-      </c>
+        <v>83.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
         <v>90</v>
       </c>
       <c r="Q4" t="n">
-        <v>84.2</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="R4" t="n">
         <v>3.45</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.22</v>
+        <v>-5.92</v>
       </c>
       <c r="T4" t="n">
         <v>14501.49</v>
@@ -936,7 +944,7 @@
         <v>180.7</v>
       </c>
       <c r="G5" t="n">
-        <v>171.66</v>
+        <v>180.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -947,23 +955,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>185</v>
+        <v>185.5</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>187.5</v>
+        <v>190.3</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>3.76</v>
+        <v>5.31</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28.08.2026 20:53:43</t>
+          <t>31.08.2026 20:54:16</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>242.2</v>
+        <v>241.4</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.9</v>
+        <v>-2.23</v>
       </c>
       <c r="O2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
         <v>252</v>
@@ -955,23 +955,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>185.5</v>
+        <v>187.5</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>3.76</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>190.3</v>
+        <v>192.9</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>5.31</v>
+        <v>6.75</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.08.2026 20:54:16</t>
+          <t>01.09.2026 20:53:58</t>
         </is>
       </c>
     </row>
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>241.4</v>
+        <v>240.1</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-2.23</v>
+        <v>-2.75</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" t="n">
         <v>252</v>
@@ -955,14 +955,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>187.5</v>
+        <v>190</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>3.76</v>
+        <v>5.15</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
         <v>192.9</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.09.2026 20:53:58</t>
+          <t>02.09.2026 20:53:57</t>
         </is>
       </c>
     </row>
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>240.1</v>
+        <v>240.6</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-2.75</v>
+        <v>-2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
         <v>252</v>
@@ -955,14 +955,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>190</v>
+        <v>191.7</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>5.15</v>
+        <v>6.09</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P5" t="n">
         <v>192.9</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02.09.2026 20:53:57</t>
+          <t>03.09.2026 20:54:02</t>
         </is>
       </c>
     </row>
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>240.6</v>
+        <v>242.4</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-2.55</v>
+        <v>-1.82</v>
       </c>
       <c r="O2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2" t="n">
         <v>252</v>
@@ -955,23 +955,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>191.7</v>
+        <v>194</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>6.09</v>
+        <v>7.36</v>
       </c>
       <c r="O5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>192.9</v>
+        <v>194.3</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>6.75</v>
+        <v>7.53</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>03.09.2026 20:54:02</t>
+          <t>04.09.2026 20:53:57</t>
         </is>
       </c>
     </row>
@@ -728,26 +728,26 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>242.4</v>
+        <v>243.9</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.82</v>
+        <v>-1.22</v>
       </c>
       <c r="O2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P2" t="n">
         <v>252</v>
       </c>
       <c r="Q2" t="n">
-        <v>237.9</v>
+        <v>236.3</v>
       </c>
       <c r="R2" t="n">
         <v>2.07</v>
       </c>
       <c r="S2" t="n">
-        <v>-3.65</v>
+        <v>-4.29</v>
       </c>
       <c r="T2" t="n">
         <v>14274.02</v>
@@ -955,23 +955,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>194</v>
+        <v>194.4</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>7.36</v>
+        <v>7.58</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
-        <v>194.3</v>
+        <v>195.8</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>7.53</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04.09.2026 20:53:57</t>
+          <t>07.09.2026 20:54:17</t>
         </is>
       </c>
     </row>
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>243.9</v>
+        <v>248.8</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-1.22</v>
+        <v>0.77</v>
       </c>
       <c r="O2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P2" t="n">
         <v>252</v>
@@ -955,14 +955,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>194.4</v>
+        <v>195</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>7.58</v>
+        <v>7.91</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
         <v>195.8</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07.09.2026 20:54:17</t>
+          <t>08.09.2026 20:53:55</t>
         </is>
       </c>
     </row>
@@ -728,23 +728,23 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>248.8</v>
+        <v>249.5</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="O2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P2" t="n">
-        <v>252</v>
+        <v>253.5</v>
       </c>
       <c r="Q2" t="n">
         <v>236.3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.07</v>
+        <v>2.67</v>
       </c>
       <c r="S2" t="n">
         <v>-4.29</v>
@@ -955,23 +955,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>195</v>
+        <v>195.5</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>7.91</v>
+        <v>8.19</v>
       </c>
       <c r="O5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>195.8</v>
+        <v>197</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>8.359999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08.09.2026 20:53:55</t>
+          <t>09.09.2026 20:53:58</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -728,14 +728,14 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>249.5</v>
+        <v>245.8</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>1.05</v>
+        <v>-0.45</v>
       </c>
       <c r="O2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P2" t="n">
         <v>253.5</v>
@@ -955,14 +955,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>195.5</v>
+        <v>195.6</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>8.19</v>
+        <v>8.25</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P5" t="n">
         <v>197</v>
@@ -988,6 +988,79 @@
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ISLEM-000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TTRAK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NORMAL AL</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>435</v>
+      </c>
+      <c r="G6" t="n">
+        <v>413.25</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>435</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>435</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>435</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>14505.48</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09.09.2026 20:53:58</t>
+          <t>10.09.2026 20:54:09</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -721,33 +721,41 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n">
+        <v>46275.375</v>
+      </c>
+      <c r="J2" t="n">
+        <v>234.56</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>245.8</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>-0.45</v>
-      </c>
+        <v>231.4</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-5</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P2" t="n">
         <v>253.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>236.3</v>
+        <v>231.4</v>
       </c>
       <c r="R2" t="n">
         <v>2.67</v>
       </c>
       <c r="S2" t="n">
-        <v>-4.29</v>
+        <v>-6.28</v>
       </c>
       <c r="T2" t="n">
         <v>14274.02</v>
@@ -955,23 +963,23 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>195.6</v>
+        <v>195.8</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>8.25</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P5" t="n">
-        <v>197</v>
+        <v>197.6</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>9.02</v>
+        <v>9.35</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1028,26 +1036,26 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>435</v>
+        <v>439.75</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>435</v>
+        <v>440.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>14505.48</v>

--- a/Yüzde.xlsx
+++ b/Yüzde.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.09.2026 20:54:09</t>
+          <t>11.09.2026 20:53:48</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -563,7 +563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -952,34 +952,42 @@
         <v>180.7</v>
       </c>
       <c r="G5" t="n">
-        <v>180.7</v>
+        <v>200.45</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AÇIK</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>KAR STOP</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>46276.375</v>
+      </c>
+      <c r="J5" t="n">
+        <v>200.45</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>IZLEYEN KAR STOP</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>195.8</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>8.359999999999999</v>
-      </c>
+        <v>205.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>10.93</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P5" t="n">
-        <v>197.6</v>
+        <v>211</v>
       </c>
       <c r="Q5" t="n">
         <v>180.7</v>
       </c>
       <c r="R5" t="n">
-        <v>9.35</v>
+        <v>16.77</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1036,14 +1044,14 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>439.75</v>
+        <v>436</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>1.09</v>
+        <v>0.23</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>440.75</v>
@@ -1069,6 +1077,79 @@
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
+        <is>
+          <t>Ertesi gün açılışta giriş</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ISLEM-000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ZRGYO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GUCLU AL</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>20</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AÇIK</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14467.25</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Ertesi gün açılışta giriş</t>
         </is>
